--- a/docs/PKI-CACERT-EXPORT.xlsx
+++ b/docs/PKI-CACERT-EXPORT.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>docker compose -f compose.yaml -f compose.build-secret.yaml build app-front app-back</t>
+          <t>docker compose -f compose.yaml -f compose.build-secret.yaml build frontend backend</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>docker compose logs app-front | grep truststore</t>
+          <t>docker compose logs frontend | grep truststore</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>docker compose -f compose.yaml -f compose.build-secret.yaml build app-front app-back</t>
+          <t>docker compose -f compose.yaml -f compose.build-secret.yaml build frontend backend</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -1133,8 +1133,8 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>docker compose logs app-front | grep 'truststore[build]'
-docker compose exec app-front cat /opt/pki/build-import.txt
+          <t>docker compose logs frontend | grep 'truststore[build]'
+docker compose exec frontend cat /opt/pki/build-import.txt
 curl -s http://localhost:8080/tls-probe/truststore | jq -r '.stores[].cacertSha256'</t>
         </is>
       </c>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>docker compose -f compose.yaml -f compose.build-secret.yaml build app-front app-back</t>
+          <t>docker compose -f compose.yaml -f compose.build-secret.yaml build frontend backend</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>docker compose restart secure-api alb mysql app-front app-back</t>
+          <t>docker compose restart secure-api alb mysql frontend backend</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>docker compose -f compose.yaml -f compose.build-secret.yaml build app-front app-back</t>
+          <t>docker compose -f compose.yaml -f compose.build-secret.yaml build frontend backend</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>docker compose logs app-front | grep truststore で [build] と [jboss] の両方を確認する</t>
+          <t>docker compose logs frontend | grep truststore で [build] と [jboss] の両方を確認する</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>docker compose restart app-front app-back。それでも直らなければ docker compose logs pki-init | grep SHA-256 と突き合わせる</t>
+          <t>docker compose restart frontend backend。それでも直らなければ docker compose logs pki-init | grep SHA-256 と突き合わせる</t>
         </is>
       </c>
     </row>
